--- a/packages/error-messages-generator/input.xlsx
+++ b/packages/error-messages-generator/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\federico.pirani\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE37472-BBA5-4BD4-9F6D-B69B8C38BC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DEFA95-0353-4102-B629-D3D38CC48DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3705" yWindow="4560" windowWidth="21600" windowHeight="11775" xr2:uid="{7726EE6F-ED96-4A6B-8942-00DA51EB3426}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{7726EE6F-ED96-4A6B-8942-00DA51EB3426}"/>
   </bookViews>
   <sheets>
     <sheet name="it" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>Copy</t>
   </si>
@@ -58,9 +58,6 @@
     <t>agreementNotFound</t>
   </si>
   <si>
-    <t>CatalogProcess</t>
-  </si>
-  <si>
     <t>ErrorCode</t>
   </si>
   <si>
@@ -83,6 +80,57 @@
   </si>
   <si>
     <t>POST /catalog/:eserviceId/agreements</t>
+  </si>
+  <si>
+    <t>Rivisto da Valentina</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Rivisto da Elena</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>catalogProcess</t>
+  </si>
+  <si>
+    <t>agreementProcess</t>
+  </si>
+  <si>
+    <t>Lalalala</t>
+  </si>
+  <si>
+    <t>Ohohohoho</t>
+  </si>
+  <si>
+    <t>Uhuhuhuh</t>
+  </si>
+  <si>
+    <t>Ihihihih</t>
+  </si>
+  <si>
+    <t>eServiceDescriptorNotFound</t>
+  </si>
+  <si>
+    <t>notValidDescriptor</t>
+  </si>
+  <si>
+    <t>POST /agreement/:eserviceId/agreements</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>ENIhihihih</t>
+  </si>
+  <si>
+    <t>ENLalalala</t>
+  </si>
+  <si>
+    <t>ENOhohohoho</t>
   </si>
 </sst>
 </file>
@@ -454,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87A42A86-5CA1-46CB-9C16-6049CC6D6CB3}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -464,103 +512,142 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <f>'Foglio su cui si lavora'!B2</f>
-        <v>Questo non è l'eservice che stavi cercando</v>
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="str">
-        <f>'Foglio su cui si lavora'!B2</f>
-        <v>Questo non è l'eservice che stavi cercando</v>
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67210B40-76DC-492B-A02A-B79D4FA771AC}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -570,21 +657,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F099D3A-4618-4FA7-A84F-5C60DD698AF5}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -593,6 +690,12 @@
       </c>
       <c r="C2" t="s">
         <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
